--- a/output/pdf_financials_xlsx/TOY.xlsx
+++ b/output/pdf_financials_xlsx/TOY.xlsx
@@ -991,10 +991,10 @@
         </is>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>-1.1</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>-10.7</v>
       </c>
       <c r="J12" s="1" t="inlineStr">
         <is>
@@ -1844,10 +1844,10 @@
         </is>
       </c>
       <c r="H27" s="3" t="n">
-        <v>262</v>
+        <v>263.1</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>340.4</v>
+        <v>351.1</v>
       </c>
       <c r="J27" s="1" t="inlineStr">
         <is>
@@ -1954,10 +1954,10 @@
         </is>
       </c>
       <c r="H29" s="3" t="n">
-        <v>295.5</v>
+        <v>296.6</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>369.3</v>
+        <v>380</v>
       </c>
       <c r="J29" s="1" t="inlineStr">
         <is>
@@ -2007,10 +2007,10 @@
         </is>
       </c>
       <c r="H30" s="3" t="n">
-        <v>14.46827262044653</v>
+        <v>14.52213082647865</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>18.27946344602287</v>
+        <v>18.80908775924367</v>
       </c>
       <c r="J30" s="1" t="inlineStr">
         <is>
@@ -2161,7 +2161,7 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>45.713</v>
       </c>
       <c r="C34" s="1" t="inlineStr">
         <is>
@@ -2169,10 +2169,10 @@
         </is>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>99.416</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>117.262</v>
       </c>
       <c r="F34" s="1" t="inlineStr">
         <is>
@@ -2271,7 +2271,7 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>45.713</v>
       </c>
       <c r="C36" s="1" t="inlineStr">
         <is>
@@ -2279,10 +2279,10 @@
         </is>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>99.416</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>117.262</v>
       </c>
       <c r="F36" s="1" t="inlineStr">
         <is>
@@ -2939,10 +2939,10 @@
         </is>
       </c>
       <c r="D48" s="3" t="n">
-        <v>120.814</v>
+        <v>21.398</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>137.762</v>
+        <v>20.5</v>
       </c>
       <c r="F48" s="1" t="inlineStr">
         <is>
@@ -37258,7 +37258,7 @@
       </c>
       <c r="D393" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E393" t="inlineStr">
@@ -39958,7 +39958,7 @@
       </c>
       <c r="D428" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E428" s="5" t="n">
@@ -84160,7 +84160,7 @@
       </c>
       <c r="D1016" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E1016" t="inlineStr">
@@ -84238,7 +84238,7 @@
       </c>
       <c r="D1017" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E1017" t="inlineStr">

--- a/output/pdf_financials_xlsx/TOY.xlsx
+++ b/output/pdf_financials_xlsx/TOY.xlsx
@@ -2328,10 +2328,8 @@
       <c r="B37" s="3" t="n">
         <v>134.618</v>
       </c>
-      <c r="C37" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C37" s="3" t="n">
+        <v>190.271</v>
       </c>
       <c r="D37" s="3" t="n">
         <v>295.068</v>
@@ -2339,36 +2337,26 @@
       <c r="E37" s="3" t="n">
         <v>369.719</v>
       </c>
-      <c r="F37" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G37" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F37" s="3" t="n">
+        <v>404</v>
+      </c>
+      <c r="G37" s="3" t="n">
+        <v>265.2</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>0</v>
+        <v>352.4</v>
       </c>
       <c r="I37" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J37" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K37" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L37" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>311</v>
+      </c>
+      <c r="J37" s="3" t="n">
+        <v>414.4</v>
+      </c>
+      <c r="K37" s="3" t="n">
+        <v>499.4</v>
+      </c>
+      <c r="L37" s="3" t="n">
+        <v>508.1</v>
       </c>
       <c r="M37" s="3" t="n">
         <v>0</v>
@@ -2493,26 +2481,20 @@
       <c r="B40" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="C40" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C40" s="3" t="n">
+        <v>11.715</v>
       </c>
       <c r="D40" s="3" t="n">
-        <v>0</v>
+        <v>69.962</v>
       </c>
       <c r="E40" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F40" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G40" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>99.438</v>
+      </c>
+      <c r="F40" s="3" t="n">
+        <v>114.918</v>
+      </c>
+      <c r="G40" s="3" t="n">
+        <v>73.40000000000001</v>
       </c>
       <c r="H40" s="3" t="n">
         <v>38.8</v>
@@ -2520,20 +2502,14 @@
       <c r="I40" s="3" t="n">
         <v>49.5</v>
       </c>
-      <c r="J40" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K40" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L40" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J40" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="K40" s="3" t="n">
+        <v>54.9</v>
+      </c>
+      <c r="L40" s="3" t="n">
+        <v>71.5</v>
       </c>
       <c r="M40" s="3" t="n">
         <v>0</v>
@@ -2554,10 +2530,10 @@
         </is>
       </c>
       <c r="D41" s="3" t="n">
-        <v>295.068</v>
+        <v>365.03</v>
       </c>
       <c r="E41" s="3" t="n">
-        <v>369.719</v>
+        <v>469.157</v>
       </c>
       <c r="F41" s="1" t="inlineStr">
         <is>
@@ -2570,20 +2546,16 @@
         </is>
       </c>
       <c r="H41" s="3" t="n">
-        <v>38.8</v>
+        <v>391.2</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>49.5</v>
-      </c>
-      <c r="J41" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K41" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>360.5</v>
+      </c>
+      <c r="J41" s="3" t="n">
+        <v>474.4</v>
+      </c>
+      <c r="K41" s="3" t="n">
+        <v>554.3</v>
       </c>
       <c r="L41" s="1" t="inlineStr">
         <is>
@@ -2939,10 +2911,10 @@
         </is>
       </c>
       <c r="D48" s="3" t="n">
-        <v>21.398</v>
+        <v>0</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>20.5</v>
+        <v>0</v>
       </c>
       <c r="F48" s="1" t="inlineStr">
         <is>
@@ -2955,10 +2927,10 @@
         </is>
       </c>
       <c r="H48" s="3" t="n">
-        <v>518.2</v>
+        <v>165.8</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>438.4</v>
+        <v>127.4</v>
       </c>
       <c r="J48" s="1" t="inlineStr">
         <is>
@@ -3829,47 +3801,35 @@
       <c r="B64" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="C64" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C64" s="3" t="n">
+        <v>55.656</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>0</v>
+        <v>92.17100000000001</v>
       </c>
       <c r="E64" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F64" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G64" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>155.519</v>
+      </c>
+      <c r="F64" s="3" t="n">
+        <v>160.6</v>
+      </c>
+      <c r="G64" s="3" t="n">
+        <v>161.4</v>
       </c>
       <c r="H64" s="3" t="n">
-        <v>0</v>
+        <v>274.7</v>
       </c>
       <c r="I64" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J64" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K64" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L64" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>153</v>
+      </c>
+      <c r="J64" s="3" t="n">
+        <v>189.2</v>
+      </c>
+      <c r="K64" s="3" t="n">
+        <v>224.2</v>
+      </c>
+      <c r="L64" s="3" t="n">
+        <v>239.6</v>
       </c>
       <c r="M64" s="3" t="n">
         <v>0</v>
@@ -3994,26 +3954,20 @@
       <c r="B67" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="C67" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C67" s="3" t="n">
+        <v>79.06100000000001</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>136.764</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F67" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G67" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>195.238</v>
+      </c>
+      <c r="F67" s="3" t="n">
+        <v>116.2</v>
+      </c>
+      <c r="G67" s="3" t="n">
+        <v>153</v>
       </c>
       <c r="H67" s="3" t="n">
         <v>476.4</v>
@@ -4021,20 +3975,14 @@
       <c r="I67" s="3" t="n">
         <v>339.4</v>
       </c>
-      <c r="J67" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K67" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L67" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J67" s="3" t="n">
+        <v>196.2</v>
+      </c>
+      <c r="K67" s="3" t="n">
+        <v>205.3</v>
+      </c>
+      <c r="L67" s="3" t="n">
+        <v>196.4</v>
       </c>
       <c r="M67" s="3" t="n">
         <v>0</v>
@@ -4055,10 +4003,10 @@
         </is>
       </c>
       <c r="D68" s="3" t="n">
-        <v>0</v>
+        <v>228.935</v>
       </c>
       <c r="E68" s="3" t="n">
-        <v>0</v>
+        <v>350.757</v>
       </c>
       <c r="F68" s="1" t="inlineStr">
         <is>
@@ -4071,20 +4019,16 @@
         </is>
       </c>
       <c r="H68" s="3" t="n">
-        <v>476.4</v>
+        <v>751.1</v>
       </c>
       <c r="I68" s="3" t="n">
-        <v>339.4</v>
-      </c>
-      <c r="J68" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K68" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>492.4</v>
+      </c>
+      <c r="J68" s="3" t="n">
+        <v>385.4</v>
+      </c>
+      <c r="K68" s="3" t="n">
+        <v>429.5</v>
       </c>
       <c r="L68" s="1" t="inlineStr">
         <is>
@@ -4181,10 +4125,10 @@
         </is>
       </c>
       <c r="H70" s="3" t="n">
-        <v>0</v>
+        <v>13.3</v>
       </c>
       <c r="I70" s="3" t="n">
-        <v>0</v>
+        <v>16.3</v>
       </c>
       <c r="J70" s="1" t="inlineStr">
         <is>
@@ -4236,10 +4180,10 @@
         </is>
       </c>
       <c r="H71" s="3" t="n">
-        <v>0</v>
+        <v>13.3</v>
       </c>
       <c r="I71" s="3" t="n">
-        <v>0</v>
+        <v>16.3</v>
       </c>
       <c r="J71" s="1" t="inlineStr">
         <is>
@@ -4440,10 +4384,10 @@
         </is>
       </c>
       <c r="D75" s="3" t="n">
-        <v>425.833</v>
+        <v>196.898</v>
       </c>
       <c r="E75" s="3" t="n">
-        <v>414.021</v>
+        <v>63.264</v>
       </c>
       <c r="F75" s="1" t="inlineStr">
         <is>
@@ -4456,10 +4400,10 @@
         </is>
       </c>
       <c r="H75" s="3" t="n">
-        <v>74.59999999999999</v>
+        <v>0</v>
       </c>
       <c r="I75" s="3" t="n">
-        <v>73.40000000000001</v>
+        <v>0</v>
       </c>
       <c r="J75" s="1" t="inlineStr">
         <is>
@@ -4739,10 +4683,10 @@
         </is>
       </c>
       <c r="H80" s="3" t="n">
-        <v>0.05672748004561003</v>
+        <v>0.06936526035727859</v>
       </c>
       <c r="I80" s="3" t="n">
-        <v>0.0441851106639839</v>
+        <v>0.05730382293762575</v>
       </c>
       <c r="J80" s="1" t="inlineStr">
         <is>
@@ -6153,7 +6097,7 @@
         <v>20.943</v>
       </c>
       <c r="E107" s="3" t="n">
-        <v>0</v>
+        <v>10.082</v>
       </c>
       <c r="F107" s="3" t="n">
         <v>0</v>
@@ -6164,10 +6108,10 @@
         </is>
       </c>
       <c r="H107" s="3" t="n">
-        <v>0</v>
+        <v>15.3</v>
       </c>
       <c r="I107" s="3" t="n">
-        <v>0</v>
+        <v>17.6</v>
       </c>
       <c r="J107" s="1" t="inlineStr">
         <is>
@@ -6303,10 +6247,10 @@
         <v>0</v>
       </c>
       <c r="D110" s="3" t="n">
-        <v>0</v>
+        <v>2.868</v>
       </c>
       <c r="E110" s="3" t="n">
-        <v>0</v>
+        <v>2.559</v>
       </c>
       <c r="F110" s="3" t="n">
         <v>0</v>
@@ -6317,10 +6261,10 @@
         </is>
       </c>
       <c r="H110" s="3" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I110" s="3" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="J110" s="1" t="inlineStr">
         <is>
@@ -6606,10 +6550,10 @@
         </is>
       </c>
       <c r="C116" s="3" t="n">
-        <v>0</v>
+        <v>-29.053</v>
       </c>
       <c r="D116" s="3" t="n">
-        <v>0</v>
+        <v>-17.542</v>
       </c>
       <c r="E116" s="3" t="n">
         <v>0</v>
@@ -36066,7 +36010,11 @@
           <t>Lease liabilities 26</t>
         </is>
       </c>
-      <c r="D377" t="inlineStr"/>
+      <c r="D377" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E377" t="inlineStr">
         <is>
           <t>-</t>
@@ -56380,7 +56328,11 @@
           <t>Accretion expense 6</t>
         </is>
       </c>
-      <c r="D645" t="inlineStr"/>
+      <c r="D645" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E645" t="inlineStr">
         <is>
           <t>-</t>
@@ -56824,7 +56776,11 @@
           <t>Share-based compensation expense 22</t>
         </is>
       </c>
-      <c r="D651" t="inlineStr"/>
+      <c r="D651" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E651" t="inlineStr">
         <is>
           <t>-</t>
@@ -63910,7 +63866,11 @@
           <t>Share-based compensation expense 17</t>
         </is>
       </c>
-      <c r="D745" t="inlineStr"/>
+      <c r="D745" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E745" t="inlineStr">
         <is>
           <t>-</t>
@@ -65844,7 +65804,11 @@
           <t>Accretion expense 6, 16</t>
         </is>
       </c>
-      <c r="D771" t="inlineStr"/>
+      <c r="D771" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E771" t="inlineStr">
         <is>
           <t>-</t>
@@ -66762,7 +66726,11 @@
           <t>Acquisition of intangible assets 12</t>
         </is>
       </c>
-      <c r="D783" t="inlineStr"/>
+      <c r="D783" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E783" t="inlineStr">
         <is>
           <t>-</t>
